--- a/web/public/dataset/01-vendor-zenith/Zenith_Quotation_ZIS-NBR-2026-1184-R2_REVISED.xlsx
+++ b/web/public/dataset/01-vendor-zenith/Zenith_Quotation_ZIS-NBR-2026-1184-R2_REVISED.xlsx
@@ -550,7 +550,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Northbridge Retail</t>
+          <t>Kaveri Retail</t>
         </is>
       </c>
     </row>
